--- a/WORD/22_12.xlsx
+++ b/WORD/22_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\WORD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72291277-9BAF-4A23-9AE0-B89720D9DD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50105731-D0BD-4399-9552-54E88B335893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16590" yWindow="2325" windowWidth="18990" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1279,6 +1279,9 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A20" s="1">
+        <v>0</v>
+      </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
       </c>
@@ -1290,6 +1293,9 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A21" s="1">
+        <v>0</v>
+      </c>
       <c r="B21" s="2" t="s">
         <v>54</v>
       </c>
@@ -1301,6 +1307,9 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A22" s="1">
+        <v>0</v>
+      </c>
       <c r="B22" s="2" t="s">
         <v>58</v>
       </c>
@@ -1312,6 +1321,9 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A23" s="1">
+        <v>0</v>
+      </c>
       <c r="B23" s="2" t="s">
         <v>60</v>
       </c>
@@ -1320,6 +1332,9 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A24" s="1">
+        <v>0</v>
+      </c>
       <c r="B24" s="2" t="s">
         <v>62</v>
       </c>
@@ -1328,6 +1343,9 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A25" s="1">
+        <v>0</v>
+      </c>
       <c r="B25" s="2" t="s">
         <v>64</v>
       </c>
@@ -1339,6 +1357,9 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A26" s="1">
+        <v>0</v>
+      </c>
       <c r="B26" s="2" t="s">
         <v>67</v>
       </c>
@@ -1350,6 +1371,9 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
+        <v>0</v>
+      </c>
       <c r="B27" s="2" t="s">
         <v>70</v>
       </c>
@@ -1361,6 +1385,9 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
+        <v>0</v>
+      </c>
       <c r="B28" s="2" t="s">
         <v>73</v>
       </c>
@@ -1369,6 +1396,9 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>0</v>
+      </c>
       <c r="B29" s="2" t="s">
         <v>75</v>
       </c>
@@ -1377,6 +1407,9 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A30" s="1">
+        <v>0</v>
+      </c>
       <c r="B30" s="2" t="s">
         <v>77</v>
       </c>
@@ -1385,6 +1418,9 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A31" s="1">
+        <v>0</v>
+      </c>
       <c r="B31" s="2" t="s">
         <v>79</v>
       </c>
@@ -1396,6 +1432,9 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A32" s="1">
+        <v>0</v>
+      </c>
       <c r="B32" s="2" t="s">
         <v>82</v>
       </c>
@@ -1406,7 +1445,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A33" s="1">
+        <v>0</v>
+      </c>
       <c r="B33" s="2" t="s">
         <v>85</v>
       </c>
@@ -1417,7 +1459,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A34" s="1">
+        <v>0</v>
+      </c>
       <c r="B34" s="2" t="s">
         <v>88</v>
       </c>
@@ -1428,7 +1473,10 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A35" s="1">
+        <v>0</v>
+      </c>
       <c r="B35" s="2" t="s">
         <v>92</v>
       </c>
@@ -1436,7 +1484,10 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A36" s="1">
+        <v>0</v>
+      </c>
       <c r="B36" s="2" t="s">
         <v>93</v>
       </c>
@@ -1444,7 +1495,10 @@
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A37" s="1">
+        <v>0</v>
+      </c>
       <c r="B37" s="2" t="s">
         <v>95</v>
       </c>
@@ -1452,7 +1506,10 @@
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A38" s="1">
+        <v>0</v>
+      </c>
       <c r="B38" s="2" t="s">
         <v>97</v>
       </c>
@@ -1460,7 +1517,10 @@
         <v>98</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A39" s="1">
+        <v>0</v>
+      </c>
       <c r="B39" s="2" t="s">
         <v>99</v>
       </c>
@@ -1471,7 +1531,10 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A40" s="1">
+        <v>0</v>
+      </c>
       <c r="B40" s="2" t="s">
         <v>102</v>
       </c>
@@ -1479,7 +1542,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A41" s="1">
+        <v>0</v>
+      </c>
       <c r="B41" s="2" t="s">
         <v>103</v>
       </c>
@@ -1490,7 +1556,10 @@
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A42" s="1">
+        <v>0</v>
+      </c>
       <c r="B42" s="2" t="s">
         <v>106</v>
       </c>
@@ -1498,7 +1567,10 @@
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A43" s="1">
+        <v>0</v>
+      </c>
       <c r="B43" s="2" t="s">
         <v>109</v>
       </c>
@@ -1506,7 +1578,10 @@
         <v>108</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A44" s="1">
+        <v>0</v>
+      </c>
       <c r="B44" s="2" t="s">
         <v>110</v>
       </c>
@@ -1514,7 +1589,10 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A45" s="1">
+        <v>0</v>
+      </c>
       <c r="B45" s="2" t="s">
         <v>112</v>
       </c>
@@ -1522,7 +1600,10 @@
         <v>113</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A46" s="1">
+        <v>0</v>
+      </c>
       <c r="B46" s="2" t="s">
         <v>114</v>
       </c>
@@ -1533,7 +1614,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A47" s="1">
+        <v>0</v>
+      </c>
       <c r="B47" s="2" t="s">
         <v>117</v>
       </c>
@@ -1541,7 +1625,10 @@
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A48" s="1">
+        <v>0</v>
+      </c>
       <c r="B48" s="2" t="s">
         <v>119</v>
       </c>
@@ -1549,7 +1636,10 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A49" s="1">
+        <v>0</v>
+      </c>
       <c r="B49" s="2" t="s">
         <v>121</v>
       </c>
@@ -1560,7 +1650,10 @@
         <v>123</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A50" s="1">
+        <v>0</v>
+      </c>
       <c r="B50" s="2" t="s">
         <v>124</v>
       </c>
@@ -1568,7 +1661,10 @@
         <v>125</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A51" s="1">
+        <v>0</v>
+      </c>
       <c r="B51" s="2" t="s">
         <v>126</v>
       </c>
@@ -1579,7 +1675,10 @@
         <v>128</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A52" s="1">
+        <v>0</v>
+      </c>
       <c r="B52" s="2" t="s">
         <v>129</v>
       </c>
@@ -1590,7 +1689,10 @@
         <v>131</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A53" s="1">
+        <v>0</v>
+      </c>
       <c r="B53" s="2" t="s">
         <v>132</v>
       </c>
@@ -1598,7 +1700,10 @@
         <v>133</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A54" s="1">
+        <v>0</v>
+      </c>
       <c r="B54" s="2" t="s">
         <v>134</v>
       </c>
@@ -1606,7 +1711,10 @@
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A55" s="1">
+        <v>0</v>
+      </c>
       <c r="B55" s="2" t="s">
         <v>136</v>
       </c>
@@ -1614,7 +1722,10 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A56" s="1">
+        <v>0</v>
+      </c>
       <c r="B56" s="2" t="s">
         <v>138</v>
       </c>
@@ -1622,7 +1733,10 @@
         <v>139</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A57" s="1">
+        <v>0</v>
+      </c>
       <c r="B57" s="2" t="s">
         <v>140</v>
       </c>
@@ -1633,7 +1747,10 @@
         <v>142</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A58" s="1">
+        <v>0</v>
+      </c>
       <c r="B58" s="2" t="s">
         <v>143</v>
       </c>
@@ -1644,7 +1761,10 @@
         <v>145</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A59" s="1">
+        <v>0</v>
+      </c>
       <c r="B59" s="2" t="s">
         <v>146</v>
       </c>
@@ -1655,7 +1775,10 @@
         <v>148</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A60" s="1">
+        <v>0</v>
+      </c>
       <c r="B60" s="2" t="s">
         <v>149</v>
       </c>
@@ -1666,7 +1789,10 @@
         <v>151</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A61" s="1">
+        <v>0</v>
+      </c>
       <c r="B61" s="2" t="s">
         <v>152</v>
       </c>
@@ -1674,7 +1800,10 @@
         <v>153</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A62" s="1">
+        <v>0</v>
+      </c>
       <c r="B62" s="2" t="s">
         <v>154</v>
       </c>
@@ -1682,7 +1811,10 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A63" s="1">
+        <v>0</v>
+      </c>
       <c r="B63" s="2" t="s">
         <v>156</v>
       </c>
@@ -1690,7 +1822,10 @@
         <v>157</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A64" s="1">
+        <v>0</v>
+      </c>
       <c r="B64" s="2" t="s">
         <v>158</v>
       </c>
@@ -1698,7 +1833,10 @@
         <v>159</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A65" s="1">
+        <v>0</v>
+      </c>
       <c r="B65" s="2" t="s">
         <v>160</v>
       </c>
@@ -1706,7 +1844,10 @@
         <v>161</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A66" s="1">
+        <v>0</v>
+      </c>
       <c r="B66" s="2" t="s">
         <v>162</v>
       </c>
@@ -1714,7 +1855,10 @@
         <v>163</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A67" s="1">
+        <v>0</v>
+      </c>
       <c r="B67" s="2" t="s">
         <v>164</v>
       </c>
@@ -1722,7 +1866,10 @@
         <v>165</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A68" s="1">
+        <v>0</v>
+      </c>
       <c r="B68" s="2" t="s">
         <v>166</v>
       </c>
